--- a/Jun-Dec-2026.xlsx
+++ b/Jun-Dec-2026.xlsx
@@ -1,13 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shaya\Desktop\jun-nov-2026\00-gitdocs\data-science\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{362CD72D-3B9A-4C8E-B6E7-271572055726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="June" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -18,9 +24,47 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+  <si>
+    <t>Day</t>
+  </si>
+  <si>
+    <t>Task1</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Task2</t>
+  </si>
+  <si>
+    <t>Task3</t>
+  </si>
+  <si>
+    <t>Task4</t>
+  </si>
+  <si>
+    <t>Task5</t>
+  </si>
+  <si>
+    <t>day15</t>
+  </si>
+  <si>
+    <t>Revision</t>
+  </si>
+  <si>
+    <t>SAS</t>
+  </si>
+  <si>
+    <t>Sql</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,16 +72,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="4" tint="0.79998168889431442"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -45,17 +103,340 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="11">
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="4" tint="0.79998168889431442"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -66,6 +447,22 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{31CED1DE-94F7-46CC-9852-D4D1E617B321}" name="Table1" displayName="Table1" ref="A1:G70" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="9" tableBorderDxfId="10" totalsRowBorderDxfId="8">
+  <autoFilter ref="A1:G70" xr:uid="{31CED1DE-94F7-46CC-9852-D4D1E617B321}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{FC770754-9770-4B66-8B88-4948E012403D}" name="Day" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{A450C606-E9C6-447F-96F5-DFBA76769A1B}" name="Date" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{50A4D27B-CA0A-41AB-A04C-0B6F5A376D5B}" name="Task1" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{5C51AAF3-9EA3-40BA-8D89-49FBF8B20EB1}" name="Task2" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{C2A8A9DE-E2F1-4E26-B029-A680A6208A21}" name="Task3" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{685F76E0-D298-4F3F-BEE8-5CA73D53E7BA}" name="Task4" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{FC588A9E-9780-44AC-A009-D068A7030938}" name="Task5" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -330,10 +727,673 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G70"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.44140625" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" customWidth="1"/>
+    <col min="3" max="7" width="17.77734375" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="3">
+        <v>46188</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="10"/>
+      <c r="G2" s="11"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="4"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="11"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="4"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="11"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="4"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="11"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="4"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="11"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="11"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="4"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="11"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="4"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="11"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="4"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="11"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="4"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="11"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="4"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="11"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="4"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="11"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="4"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="11"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="4"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="11"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="4"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="11"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="4"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="11"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="4"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="11"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="11"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="4"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="11"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="4"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="11"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="4"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="11"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="4"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="11"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="4"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="11"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="4"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="11"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="4"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="11"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="4"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="11"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="4"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="11"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="4"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="11"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="4"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="11"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="4"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="11"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="4"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="11"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="4"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="11"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="4"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="11"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="4"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="11"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" s="4"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="11"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="4"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="11"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="4"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10"/>
+      <c r="G38" s="11"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="4"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="10"/>
+      <c r="F39" s="10"/>
+      <c r="G39" s="11"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" s="4"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="10"/>
+      <c r="E40" s="10"/>
+      <c r="F40" s="10"/>
+      <c r="G40" s="11"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="4"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="10"/>
+      <c r="G41" s="11"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" s="4"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="10"/>
+      <c r="D42" s="10"/>
+      <c r="E42" s="10"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="11"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="4"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="10"/>
+      <c r="D43" s="10"/>
+      <c r="E43" s="10"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="11"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="4"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="10"/>
+      <c r="E44" s="10"/>
+      <c r="F44" s="10"/>
+      <c r="G44" s="11"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" s="4"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="10"/>
+      <c r="D45" s="10"/>
+      <c r="E45" s="10"/>
+      <c r="F45" s="10"/>
+      <c r="G45" s="11"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="4"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="10"/>
+      <c r="E46" s="10"/>
+      <c r="F46" s="10"/>
+      <c r="G46" s="11"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" s="4"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="10"/>
+      <c r="D47" s="10"/>
+      <c r="E47" s="10"/>
+      <c r="F47" s="10"/>
+      <c r="G47" s="11"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" s="4"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="10"/>
+      <c r="E48" s="10"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="11"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="4"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="10"/>
+      <c r="D49" s="10"/>
+      <c r="E49" s="10"/>
+      <c r="F49" s="10"/>
+      <c r="G49" s="11"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="4"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="10"/>
+      <c r="D50" s="10"/>
+      <c r="E50" s="10"/>
+      <c r="F50" s="10"/>
+      <c r="G50" s="11"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="4"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="10"/>
+      <c r="D51" s="10"/>
+      <c r="E51" s="10"/>
+      <c r="F51" s="10"/>
+      <c r="G51" s="11"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="4"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="10"/>
+      <c r="E52" s="10"/>
+      <c r="F52" s="10"/>
+      <c r="G52" s="11"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="4"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="10"/>
+      <c r="D53" s="10"/>
+      <c r="E53" s="10"/>
+      <c r="F53" s="10"/>
+      <c r="G53" s="11"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A54" s="4"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="10"/>
+      <c r="D54" s="10"/>
+      <c r="E54" s="10"/>
+      <c r="F54" s="10"/>
+      <c r="G54" s="11"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A55" s="4"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="10"/>
+      <c r="D55" s="10"/>
+      <c r="E55" s="10"/>
+      <c r="F55" s="10"/>
+      <c r="G55" s="11"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A56" s="4"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="10"/>
+      <c r="D56" s="10"/>
+      <c r="E56" s="10"/>
+      <c r="F56" s="10"/>
+      <c r="G56" s="11"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57" s="4"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="10"/>
+      <c r="D57" s="10"/>
+      <c r="E57" s="10"/>
+      <c r="F57" s="10"/>
+      <c r="G57" s="11"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58" s="4"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="10"/>
+      <c r="D58" s="10"/>
+      <c r="E58" s="10"/>
+      <c r="F58" s="10"/>
+      <c r="G58" s="11"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A59" s="4"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="10"/>
+      <c r="D59" s="10"/>
+      <c r="E59" s="10"/>
+      <c r="F59" s="10"/>
+      <c r="G59" s="11"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A60" s="4"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="10"/>
+      <c r="E60" s="10"/>
+      <c r="F60" s="10"/>
+      <c r="G60" s="11"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A61" s="4"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="10"/>
+      <c r="D61" s="10"/>
+      <c r="E61" s="10"/>
+      <c r="F61" s="10"/>
+      <c r="G61" s="11"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62" s="4"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="10"/>
+      <c r="D62" s="10"/>
+      <c r="E62" s="10"/>
+      <c r="F62" s="10"/>
+      <c r="G62" s="11"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63" s="4"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="10"/>
+      <c r="D63" s="10"/>
+      <c r="E63" s="10"/>
+      <c r="F63" s="10"/>
+      <c r="G63" s="11"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64" s="4"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="10"/>
+      <c r="D64" s="10"/>
+      <c r="E64" s="10"/>
+      <c r="F64" s="10"/>
+      <c r="G64" s="11"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A65" s="4"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="10"/>
+      <c r="D65" s="10"/>
+      <c r="E65" s="10"/>
+      <c r="F65" s="10"/>
+      <c r="G65" s="11"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A66" s="4"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="10"/>
+      <c r="D66" s="10"/>
+      <c r="E66" s="10"/>
+      <c r="F66" s="10"/>
+      <c r="G66" s="11"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A67" s="4"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="10"/>
+      <c r="D67" s="10"/>
+      <c r="E67" s="10"/>
+      <c r="F67" s="10"/>
+      <c r="G67" s="11"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A68" s="4"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="10"/>
+      <c r="D68" s="10"/>
+      <c r="E68" s="10"/>
+      <c r="F68" s="10"/>
+      <c r="G68" s="11"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A69" s="4"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="10"/>
+      <c r="D69" s="10"/>
+      <c r="E69" s="10"/>
+      <c r="F69" s="10"/>
+      <c r="G69" s="11"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A70" s="8"/>
+      <c r="B70" s="9"/>
+      <c r="C70" s="12"/>
+      <c r="D70" s="12"/>
+      <c r="E70" s="12"/>
+      <c r="F70" s="12"/>
+      <c r="G70" s="13"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>